--- a/DXLibProject_Start/Data/CSV/StairModel.xlsx
+++ b/DXLibProject_Start/Data/CSV/StairModel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA798CE-1CFF-4372-8D46-E9017DC20289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47CE64A-087B-4150-B815-E8184699C034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -51,11 +52,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Resource\\Map</t>
+    <t>Resource\\Map\\</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>stair.mv1</t>
+    <t>stairs.mv1</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -433,6 +434,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>